--- a/experiments/experiment_sheets/experiments_c.xlsx
+++ b/experiments/experiment_sheets/experiments_c.xlsx
@@ -61,7 +61,7 @@
     <t>H_ins</t>
   </si>
   <si>
-    <t>Δφ (100m)</t>
+    <t>Δφ (100)</t>
   </si>
 </sst>
 </file>
@@ -119,7 +119,7 @@
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="7.28515625" customWidth="true"/>
     <col min="9" max="9" width="6" customWidth="true"/>
-    <col min="10" max="10" width="14.7109375" customWidth="true"/>
+    <col min="10" max="10" width="11.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -183,7 +183,7 @@
         <v>25</v>
       </c>
       <c r="J2" s="0">
-        <v>0.0038576268939408466</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="3">
@@ -215,7 +215,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="0">
-        <v>0.0047575190880081667</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="4">
@@ -247,7 +247,7 @@
         <v>25</v>
       </c>
       <c r="J4" s="0">
-        <v>0.016415045485994994</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="5">
@@ -279,7 +279,7 @@
         <v>20</v>
       </c>
       <c r="J5" s="0">
-        <v>0.0048398495610328506</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="6">
@@ -311,7 +311,7 @@
         <v>25</v>
       </c>
       <c r="J6" s="0">
-        <v>0.0021352303031426344</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="7">
@@ -343,7 +343,7 @@
         <v>47</v>
       </c>
       <c r="J7" s="0">
-        <v>0.0014825315993539335</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="8">
@@ -375,7 +375,7 @@
         <v>25</v>
       </c>
       <c r="J8" s="0">
-        <v>0.054678070708187088</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="9">
@@ -407,7 +407,7 @@
         <v>46</v>
       </c>
       <c r="J9" s="0">
-        <v>0.060315264971245591</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="10">
@@ -439,7 +439,7 @@
         <v>10</v>
       </c>
       <c r="J10" s="0">
-        <v>51.506656588324532</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="11">
@@ -471,7 +471,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="0">
-        <v>51.051434560033854</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="12">
@@ -503,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="J12" s="0">
-        <v>90.54100643955185</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="13">
@@ -535,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="J13" s="0">
-        <v>89.79116266680991</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         <v>6</v>
       </c>
       <c r="J14" s="0">
-        <v>53.74922360798719</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="15">
@@ -599,7 +599,7 @@
         <v>49</v>
       </c>
       <c r="J15" s="0">
-        <v>53.217028362325692</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="16">
@@ -631,7 +631,7 @@
         <v>6</v>
       </c>
       <c r="J16" s="0">
-        <v>93.212556779942474</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="17">
@@ -663,7 +663,7 @@
         <v>49</v>
       </c>
       <c r="J17" s="0">
-        <v>92.311692689403358</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
   </sheetData>
